--- a/catalogo/catalogo.xlsx
+++ b/catalogo/catalogo.xlsx
@@ -478,9 +478,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -536,9 +533,6 @@
           <t>Los demás campos de cada hoja son los huecos {campo} de su plantilla de pedido (hoja Plantillas).</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1843,7 +1837,7 @@
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>referencia_pared.png</t>
+          <t>referencia_pared.webp</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -1951,7 +1945,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>referencia_ventana.png</t>
+          <t>referencia_ventana.webp</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -2055,7 +2049,7 @@
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>referencia_piso.png</t>
+          <t>referencia_piso.webp</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -2163,7 +2157,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>referencia_sillones.png</t>
+          <t>referencia_sillones.webp</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -2271,7 +2265,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>referencia_mesa.png</t>
+          <t>referencia_mesa.webp</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -2379,7 +2373,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>referencia_alfombra.png</t>
+          <t>referencia_alfombra.webp</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -2487,7 +2481,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>referencia_estante.png</t>
+          <t>referencia_estante.webp</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -2830,7 +2824,7 @@
         <is>
           <t>ADJUNTAR (solo estos tres archivos de esta carpeta):
   1. {clave}_echado_color.png      (el boceto de la pose)
-  2. {clave}_parado.png            (la ilustración de pie que ya tienes: para que salga EL MISMO gato)
+  2. {clave}_parado.webp            (la ilustración de pie que ya tienes: para que salga EL MISMO gato)
   3. foto_referencia.jpg
 PEGAR ESTE TEXTO:
 Genera ahora una imagen. No describas, no esperes más material.
@@ -2849,9 +2843,9 @@
         <is>
           <t>ADJUNTAR (de esta carpeta):
   1. {clave}_sentado_color.png     (el boceto de la pose: sentado DE FRENTE, como la foto de pose)
-  2. {clave}_parado.png            (la ilustración de pie que ya tienes: para que salga EL MISMO gato)
+  2. {clave}_parado.webp            (la ilustración de pie que ya tienes: para que salga EL MISMO gato)
   3. foto_referencia.jpg
-  4. (opcional) Referencias\pose_sentado_referencia.png   (SOLO como guía de la pose: es OTRO gato, el pelaje no es ese)
+  4. (opcional) Referencias\pose_sentado_referencia.webp   (SOLO como guía de la pose: es OTRO gato, el pelaje no es ese)
 PEGAR ESTE TEXTO:
 Genera ahora una imagen. No describas, no esperes más material.
 Redibuja el boceto adjunto (el gato sentado DE FRENTE) como una ilustración terminada: misma pose, el gato SENTADO erguido mirando a quien lo mira, el cuerpo ALTO Y ESTRECHO en forma de huevo (el doble de alto que de ancho, como en el boceto: nada de gato redondo), la cabeza como un tercio de la altura, el pecho alto, las ancas redondas asomando a los dos lados abajo, las dos patas delanteras LARGAS, rectas y juntas en el medio con las zarpas apoyadas en el suelo, la cola enroscada en el suelo a un lado, la cabeza erguida, las orejas atentas y los ojos abiertos; 1024 x 683 píxeles, fondo transparente. Es EL MISMO gato de la otra imagen adjunta (la ilustración de pie): mismo pelaje, mismos colores, misma pincelada. Pelaje: {pelaje_es}
